--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -594,27 +594,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -624,28 +624,32 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年秋季至冬季报名</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>通常每年2月</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comap.com/contests/mcm-icm</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -657,27 +661,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,64 +691,64 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -754,115 +758,119 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>CUMCM通讯2026年第1期（总第67期）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -872,56 +880,56 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -931,56 +939,56 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -990,56 +998,56 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1049,56 +1057,56 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1108,36 +1116,36 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1147,17 +1155,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1167,7 +1175,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1175,150 +1183,142 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通常每年秋季至冬季报名</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>通常每年2月</t>
-        </is>
-      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>每年春季至暑期关注学校通知</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>通常每年9月</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/special/dzjs</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1368,24 +1368,16 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1397,58 +1389,54 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026年</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1448,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CUMCM通讯2026年第1期（总第67期）</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1490,24 +1478,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1519,27 +1507,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1549,24 +1537,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1578,27 +1566,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1608,24 +1596,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1625,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1667,24 +1655,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1696,54 +1684,58 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1755,54 +1747,62 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1921,22 +1921,22 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年4月至6月启动</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年4月至10月</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至6月启动</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至10月</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2010,27 +2010,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15838/</t>
@@ -3054,7 +3058,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>92</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -3086,51 +3090,55 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年秋季至冬季报名</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年2月</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季公布</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>获奖证书</t>
+          <t>国际竞赛证书</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>中国统计教育学会</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>COMAP</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comap.com/contests/mcm-icm</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>中</t>
@@ -3138,7 +3146,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -3158,17 +3166,17 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -3186,7 +3194,11 @@
           <t>种子数据</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comap.com/contests/mcm-icm</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
@@ -3196,57 +3208,53 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>部分赛题设置奖金</t>
-        </is>
-      </c>
+          <t>通常赛后数月公示</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>获奖证书</t>
+          <t>国家级/赛区级获奖证书</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>中国计算机学会</t>
+          <t>中国工业与应用数学学会</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3256,7 +3264,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3276,17 +3284,17 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -3296,7 +3304,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -3306,7 +3314,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -3318,33 +3326,41 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3354,7 +3370,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3374,37 +3390,37 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -3416,22 +3432,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>CUMCM通讯2026年第1期（总第67期）</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -3442,7 +3458,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3452,17 +3468,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3472,37 +3488,37 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -3514,22 +3530,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -3540,7 +3556,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3550,7 +3566,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3570,37 +3586,37 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -3612,22 +3628,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -3638,7 +3654,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3648,7 +3664,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3668,37 +3684,37 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -3710,22 +3726,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -3736,7 +3752,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3746,7 +3762,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3766,37 +3782,37 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -3808,22 +3824,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -3834,7 +3850,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3844,7 +3860,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3864,37 +3880,37 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -3906,22 +3922,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -3932,7 +3948,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3942,7 +3958,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3962,37 +3978,37 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -4004,7 +4020,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4014,60 +4030,84 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>部分赛题设置奖金</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>中国计算机学会</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
           <t>100</t>
@@ -4075,17 +4115,17 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4102,113 +4142,93 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions/1100</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>通常每年秋季至冬季报名</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>通常每年2月</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季公布</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>国际竞赛证书</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>COMAP</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -4220,113 +4240,93 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/special/dzjs</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>每年春季至暑期关注学校通知</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>通常每年9月</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>通常赛后数月公示</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>国家级/赛区级获奖证书</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>中国工业与应用数学学会</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4353,68 +4353,48 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>中国大学生计算机设计大赛组织委员会</t>
-        </is>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -4434,17 +4414,17 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -4456,83 +4436,75 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026年</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4540,17 +4512,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -4562,22 +4534,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CUMCM通讯2026年第1期（总第67期）</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -4588,49 +4560,49 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4638,17 +4610,17 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
@@ -4660,22 +4632,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -4686,49 +4658,49 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4736,17 +4708,17 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -4758,22 +4730,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -4784,49 +4756,49 @@
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4834,17 +4806,17 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -4856,22 +4828,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -4882,49 +4854,49 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4932,17 +4904,17 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -4954,75 +4926,91 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>中国统计教育学会</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -5030,19 +5018,15 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
+          <t>种子数据</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
@@ -5052,73 +5036,93 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>中国商业统计学会</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>58</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5128,17 +5132,17 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -5150,7 +5154,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -5160,12 +5164,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5191,12 +5195,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>中国商业统计学会</t>
+          <t>教育部高等学校电子商务类专业教学指导委员会</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -5216,7 +5220,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5231,12 +5235,12 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5256,7 +5260,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -5268,12 +5272,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -5283,25 +5287,29 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>通常每年4月至6月启动</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>通常每年4月至10月</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>部分赛道有奖金/扶持资源</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -5309,12 +5317,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>教育部高等学校电子商务类专业教学指导委员会</t>
+          <t>教育部等部门</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5324,17 +5332,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -5364,7 +5372,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -5374,7 +5382,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
@@ -5386,7 +5394,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -5401,17 +5409,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至6月启动</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至10月</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5419,11 +5427,7 @@
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>部分赛道有奖金/扶持资源</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -5431,12 +5435,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>教育部等部门</t>
+          <t>共青团中央等单位</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -5496,7 +5500,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -5508,22 +5512,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5549,12 +5553,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>共青团中央等单位</t>
+          <t>中国大学生计算机设计大赛组织委员会</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5569,12 +5573,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -5589,22 +5593,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -5614,7 +5618,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
@@ -6281,7 +6285,11 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -446,7 +446,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至6月启动</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至10月</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2491,11 +2491,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15838/</t>
@@ -2615,7 +2611,7 @@
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2025.11.03</t>
+          <t>2025.11.15</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2676,7 +2672,11 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules</t>
@@ -2825,7 +2825,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -5292,12 +5292,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至6月启动</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>通常每年4月至10月</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6285,11 +6285,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -6487,7 +6483,7 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2025.11.03</t>
+          <t>2025.11.15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -6587,7 +6583,11 @@
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -3083,7 +3083,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流云南站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15834/</t>
+          <t>https://www.tiaozhanbei.net/article/15837/</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（三）</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/Iu5xv-Nhr9wm7kit8_404Q?scene=1&amp;click_id=5</t>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流云南站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -6089,14 +6089,10 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>邀请有关省份参加，持续做好竞赛培训交流工作，助力更多高校师生提升备赛水平</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15834/</t>
+          <t>https://www.tiaozhanbei.net/article/15837/</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -6161,14 +6157,14 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6194,7 +6190,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -6259,14 +6255,14 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -6292,7 +6288,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -6357,14 +6353,14 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（三）</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6390,7 +6386,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/Iu5xv-Nhr9wm7kit8_404Q?scene=1&amp;click_id=5</t>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -6455,7 +6451,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6553,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6667,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6769,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6867,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -6089,10 +6089,14 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>共青团中央、教育部、人力资源社会保障部、中国科协、 中国科学院、 中国社会科学院、中国工程院、全国学联、辽宁省人民政府 承办单位： 大连理工大学、共青团辽宁省委 二、竞赛主题 青春</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -6157,7 +6161,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6259,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6357,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6455,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6557,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6671,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6773,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6871,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="评分说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'本周推荐'!$A$1:$M$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整数据'!$A$1:$X$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'本周推荐'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整数据'!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'评分说明'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -728,58 +728,62 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -791,27 +795,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CUMCM通讯2026年第1期（总第67期）</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -821,24 +825,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -850,54 +854,54 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/special/dzjs</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -909,27 +913,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -939,24 +943,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -968,27 +972,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -998,24 +1002,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1027,27 +1031,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1057,24 +1061,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1086,27 +1090,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1116,24 +1120,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1149,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1155,12 +1159,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1183,16 +1187,8 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://www.datafountain.cn/competitions</t>
@@ -1200,7 +1196,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1208,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1254,7 +1250,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1271,7 +1267,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1281,12 +1277,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1296,7 +1292,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1306,19 +1302,23 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1330,54 +1330,54 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1389,54 +1389,62 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1448,54 +1456,62 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1507,54 +1523,62 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1566,71 +1590,79 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1640,12 +1672,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1655,41 +1687,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1699,27 +1739,27 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1732,27 +1772,31 @@
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1762,17 +1806,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1782,64 +1826,56 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1854,34 +1890,34 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1916,22 +1952,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1943,12 +1971,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1958,12 +1986,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1983,22 +2011,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2015,22 +2035,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2040,7 +2060,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2050,27 +2070,23 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2098,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2097,7 +2113,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2117,22 +2133,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2149,7 +2157,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2164,7 +2172,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2184,14 +2192,18 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2025.11.15</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2208,22 +2220,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2233,7 +2245,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2243,27 +2255,23 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2283,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>竞赛简介</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,12 +2293,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2317,7 +2325,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2334,22 +2342,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2359,7 +2367,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2376,438 +2384,17 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯动态</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>2025.11.15</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（大挑）</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>竞赛简介</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>英语与财经表达类</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chinaneccs.cn/</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
           <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M38"/>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2818,14 +2405,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
@@ -2842,7 +2429,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
     <col width="38" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
@@ -3083,7 +2670,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -3201,7 +2788,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -3228,7 +2815,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3319,90 +2906,106 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>部分赛题设置奖金</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>中国计算机学会</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>http://cumcm.cnki.net</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3410,44 +3013,44 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CUMCM通讯2026年第1期（总第67期）</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -3458,49 +3061,49 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3508,44 +3111,44 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -3556,49 +3159,49 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/special/dzjs</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3606,44 +3209,44 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -3654,49 +3257,49 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3704,44 +3307,44 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -3752,49 +3355,49 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3802,44 +3405,44 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -3850,49 +3453,49 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3900,44 +3503,44 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -3948,49 +3551,49 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -3998,29 +3601,29 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4030,44 +3633,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>部分赛题设置奖金</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>中国计算机学会</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://www.datafountain.cn/competitions</t>
@@ -4120,12 +3699,12 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4135,14 +3714,14 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4168,7 +3747,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -4233,14 +3812,14 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4250,25 +3829,41 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>中国统计教育学会</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>低</t>
@@ -4281,19 +3876,19 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -4306,7 +3901,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>94</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4316,44 +3911,40 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
+          <t>种子数据</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -4361,10 +3952,14 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>共青团中央、教育部、人力资源社会保障部、中国科协、 中国科学院、 中国社会科学院、中国工程院、全国学联、辽宁省人民政府 承办单位： 大连理工大学、共青团辽宁省委 二、竞赛主题 青春</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -4374,37 +3969,37 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -4414,55 +4009,75 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>挑战杯官网</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>中国商业统计学会</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4472,37 +4087,37 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>58</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4512,55 +4127,75 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>教育部高等学校电子商务类专业教学指导委员会</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4570,37 +4205,37 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4610,95 +4245,119 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>部分赛道有奖金/扶持资源</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>教育部等部门</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://cy.ncss.cn/</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -4708,95 +4367,115 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>共青团中央等单位</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -4806,34 +4485,34 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4843,18 +4522,38 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>中国大学生计算机设计大赛组织委员会</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4864,7 +4563,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,12 +4578,12 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -4894,44 +4593,44 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>84</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4941,7 +4640,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4967,10 +4666,14 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中国统计教育学会</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+          <t>共青团中央等单位</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>低</t>
@@ -4978,47 +4681,47 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -5026,22 +4729,26 @@
           <t>种子数据</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5051,38 +4758,18 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>中国商业统计学会</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5092,17 +4779,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5117,69 +4804,69 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>全国大学生创业服务网</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5195,12 +4882,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>教育部高等学校电子商务类专业教学指导委员会</t>
+          <t>高等学校大学外语教学研究会</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -5210,17 +4897,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5245,12 +4932,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -5260,19 +4947,19 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5290,39 +4977,19 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>部分赛道有奖金/扶持资源</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>教育部等部门</t>
+          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights Reser</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5362,12 +5029,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5377,24 +5044,24 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>挑战杯官网</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -5404,161 +5071,125 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>共青团中央等单位</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>P2 可选参加</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>种子数据</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>2009-20</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>中国大学生计算机设计大赛组织委员会</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5573,12 +5204,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -5593,12 +5224,12 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -5608,29 +5239,29 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>挑战杯官网</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -5645,110 +5276,90 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>共青团中央等单位</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>种子数据</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5763,18 +5374,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2025.11.15</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -5814,7 +5429,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -5829,70 +5444,66 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>全国大学生创业服务网</t>
+          <t>挑战杯官网</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>获奖证书</t>
+          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>高等学校大学外语教学研究会</t>
+          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5907,12 +5518,12 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -5932,7 +5543,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -5942,29 +5553,29 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>挑战杯官网</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>竞赛简介</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5974,12 +5585,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -5989,99 +5600,99 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>共青团中央 中国科协 教育部 中国社会科学院 中国工程院 全国学联 Copyright © 2009-2025 All Rights Reserved. 挑战杯全国大学生课外学术科</t>
+          <t>的全国性的大学生课外学术实践竞赛，竞赛官方网站为 www.tiaozhanbei.net</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/focus</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -6089,14 +5700,10 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>共青团中央、教育部、人力资源社会保障部、中国科协、 中国科学院、 中国社会科学院、中国工程院、全国学联、辽宁省人民政府 承办单位： 大连理工大学、共青团辽宁省委 二、竞赛主题 青春</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -6111,12 +5718,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -6146,737 +5753,27 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯动态</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>2025.11.15</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（大挑）</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>竞赛简介</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>的全国性的大学生课外学术实践竞赛，竞赛官方网站为 www.tiaozhanbei.net</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯官网</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>英语与财经表达类</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chinaneccs.cn/</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>含金量价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>全国大学生英语竞赛</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chinaneccs.cn/</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X38"/>
+  <autoFilter ref="A1:X31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2074,11 +2074,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15839/</t>
@@ -2670,7 +2666,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2784,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2902,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3024,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3122,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3220,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3318,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3416,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3514,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3612,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3710,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3808,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3918,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4020,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4138,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4256,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4378,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4496,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4732,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4830,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4948,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4980,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights Reser</t>
+          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国科学院 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -5054,7 +5050,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5148,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5178,11 +5174,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -5254,7 +5246,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5344,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5446,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5560,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5662,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5760,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2015,7 +2015,11 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15838/</t>
@@ -2666,7 +2670,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2788,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3028,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3126,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3224,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3322,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3420,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3518,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3714,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3812,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3922,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4024,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4142,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4260,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4382,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4500,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4618,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4736,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4952,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5054,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5080,11 @@
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -5148,7 +5156,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5254,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5352,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5454,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5568,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5670,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5768,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1739,42 +1739,38 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1791,22 +1787,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1816,7 +1812,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1826,19 +1822,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1854,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1888,24 +1892,16 @@
           <t>40</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季初赛/决赛</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1913,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1942,7 +1938,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1952,19 +1948,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季初赛/决赛</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1986,12 +1990,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2017,12 +2021,12 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2039,7 +2043,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
+          <t>挑战杯丨江苏“挑战杯”参赛大学生人数项目数创历史新高！</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2049,12 +2053,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2081,7 +2085,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
+          <t>https://www.tiaozhanbei.net/article/15847/</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2140,7 +2144,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2198,7 +2202,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2025.11.15</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2670,7 +2674,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2792,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3032,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3130,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3326,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3424,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3718,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3816,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3926,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4028,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4264,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4386,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4408,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4414,15 +4418,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -4500,29 +4508,29 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4532,15 +4540,19 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -4548,12 +4560,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛组织委员会</t>
+          <t>共青团中央等单位</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4568,12 +4580,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -4588,22 +4600,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -4613,19 +4625,19 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -4640,136 +4652,144 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>共青团中央等单位</t>
+          <t>，东北林业大学承办，中国工商银行黑龙江省分行支持的第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛开幕式在东北林业大学举办</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>种子数据</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>中国大学生计算机设计大赛组织委员会</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4784,12 +4804,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -4804,12 +4824,12 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -4819,75 +4839,55 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>全国大学生创业服务网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>通常每年春季初赛/决赛</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>高等学校大学外语教学研究会</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -4937,59 +4937,75 @@
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>全国大学生创业服务网</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季初赛/决赛</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国科学院 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights</t>
+          <t>高等学校大学外语教学研究会</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5004,12 +5020,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -5029,7 +5045,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -5039,29 +5055,29 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -5071,27 +5087,31 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国科学院 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -5156,14 +5176,14 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
+          <t>挑战杯丨江苏“挑战杯”参赛大学生人数项目数创历史新高！</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5173,23 +5193,31 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>，江苏大学、共青团镇江市委承办</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
+          <t>https://www.tiaozhanbei.net/article/15847/</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5254,14 +5282,14 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -5284,10 +5312,14 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>，浙江工业大学承办</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5352,7 +5384,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5412,7 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2025.11.15</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -5454,7 +5486,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5600,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5702,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5800,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1667,39 +1667,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2026.06.19</t>
@@ -1707,7 +1703,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1724,32 +1720,32 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1759,23 +1755,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨江苏“挑战杯”参赛大学生人数项目数创历史新高！</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15847/</t>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2141,10 +2141,14 @@
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2161,7 +2165,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2202,12 +2206,12 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2224,7 +2228,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2796,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3036,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3134,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3232,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3330,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3428,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3526,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3722,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3820,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3930,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4032,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4150,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4268,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4390,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4412,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4426,11 +4430,7 @@
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
-        </is>
-      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -4508,14 +4508,14 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4525,153 +4525,149 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2026.06.19</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>共青团中央等单位</t>
+          <t>，东北林业大学承办，中国工商银行黑龙江省分行支持的第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛开幕式在东北林业大学举办</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>P2 可选参加</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>种子数据</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>，东北林业大学承办，中国工商银行黑龙江省分行支持的第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛开幕式在东北林业大学举办</t>
+          <t>中国大学生计算机设计大赛组织委员会</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4681,17 +4677,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -4706,12 +4702,12 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>84</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -4721,44 +4717,44 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4768,7 +4764,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4784,12 +4780,12 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛组织委员会</t>
+          <t>共青团中央等单位</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4804,12 +4800,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -4824,12 +4820,12 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -4839,7 +4835,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -4849,12 +4845,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4948,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5066,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -5176,14 +5172,14 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨江苏“挑战杯”参赛大学生人数项目数创历史新高！</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5193,31 +5189,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>成果申报南京市领军型人才项目，获得130万元启动资金和免费办公场地。如今，他的公司已成长为国家高新技术企业，专注泵系统节能，技术达国际先进水平。“很多人问我创业最难的是什么？我说是‘被看见’。‘挑战杯’让我的项目被资本看见、被政策看见。而江</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>，江苏大学、共青团镇江市委承办</t>
+          <t>，浙江工业大学承办</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15847/</t>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5282,14 +5274,14 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -5308,18 +5300,18 @@
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>，浙江工业大学承办</t>
-        </is>
-      </c>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5384,14 +5376,14 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5412,16 +5404,28 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -5486,14 +5490,14 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -5520,12 +5524,12 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
+          <t>及良好市场潜力和发展前景的优秀项目，给予奖励；组织项目和成果的交流、展览、转化活动。在符合竞赛宗旨、具有良好导向的前提下，竞赛可设立专项赛事及配套交流活动，具体规则另行制定和颁布。 第四条 竞赛由校级、省级、全国三级赛制构成。校级初赛由各高</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
+          <t>或专利技术所有人的书面授权许可、项目鉴定证书、专利证书等； （七）对于涉及已工商注册企业的项目，报名时应当提交相应证明材料（包括但不限于单位概况、法定代表人情况、加载统一社会信用代码的营业执照、股权结构等），项目负责人必须为企业法定代表人。</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5535,7 +5539,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5600,7 +5604,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5706,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5804,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="评分说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'本周推荐'!$A$1:$M$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整数据'!$A$1:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'本周推荐'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整数据'!$A$1:$X$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'评分说明'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -728,27 +728,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -758,32 +758,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -795,27 +787,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -825,24 +817,28 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -854,54 +850,54 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -913,27 +909,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -943,24 +939,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -972,27 +968,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1002,24 +998,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1031,27 +1027,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,24 +1057,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1090,27 +1086,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1120,24 +1116,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1145,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1187,8 +1183,16 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://www.datafountain.cn/competitions</t>
@@ -1196,7 +1200,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1250,7 +1254,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1267,7 +1271,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1277,12 +1281,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1302,23 +1306,19 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/special/dzjs</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1330,54 +1330,54 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1389,62 +1389,54 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1456,62 +1448,54 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1523,62 +1507,54 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -1590,157 +1566,145 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1750,12 +1714,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1768,31 +1732,27 @@
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1802,17 +1762,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1822,7 +1782,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1832,54 +1792,54 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1892,43 +1852,51 @@
           <t>40</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1938,7 +1906,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1953,34 +1921,34 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1995,7 +1963,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2015,10 +1983,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2026.06.19</t>
@@ -2043,7 +2015,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2063,29 +2035,33 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2102,22 +2078,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2127,7 +2103,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2137,23 +2113,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2145,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2180,7 +2160,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2200,18 +2180,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2228,7 +2212,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（小挑）</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2243,7 +2227,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2263,18 +2247,14 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2291,22 +2271,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>竞赛简介</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2316,7 +2296,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2326,19 +2306,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季初赛/决赛</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
@@ -2350,59 +2338,488 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯动态</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>竞赛简介</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/focus</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>英语与财经表达类</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:M38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2413,14 +2830,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
@@ -2437,7 +2854,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="38" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
@@ -2678,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2823,7 +3240,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2914,74 +3331,54 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>部分赛题设置奖金</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>中国计算机学会</t>
+          <t>中国工业与应用数学学会（CSIAM） 承办单位：CSIAM数学模型专业委员会（代章） 全国大学生数学建模竞赛组委会 太原理工大学 协办单位：山西省工业与应用数学学会 2026年5月</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2996,22 +3393,22 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3021,65 +3418,73 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3094,22 +3499,22 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -3119,44 +3524,44 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -3167,47 +3572,47 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3217,44 +3622,44 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -3265,17 +3670,17 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1098</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3290,22 +3695,22 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3315,44 +3720,44 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>基于人工智能的闽江流域水情预报</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -3363,17 +3768,17 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1102</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3388,22 +3793,22 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -3413,44 +3818,44 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>多模态BadCase极限挑战赛</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -3461,17 +3866,17 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1104</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3486,22 +3891,22 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3511,44 +3916,44 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -3559,17 +3964,17 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3584,22 +3989,22 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3609,29 +4014,29 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>全国大学生数学建模竞赛官网</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3641,20 +4046,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>部分赛题设置奖金</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>中国计算机学会</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://www.datafountain.cn/competitions</t>
@@ -3707,12 +4136,12 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>CCF BDCI</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -3722,14 +4151,14 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>盲区突围：模型BadCase极限挑战赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3755,7 +4184,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1097</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3820,14 +4249,14 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>“睿创杯”第二届高校创新创业大赛</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3837,41 +4266,25 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>中国统计教育学会</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/special/dzjs</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>低</t>
@@ -3884,12 +4297,12 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3909,7 +4322,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3919,40 +4332,44 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr"/>
+          <t>CCF BDCI</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
+          <t>中文开源数据集驱动中文大模型智能跃迁挑战赛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -3960,14 +4377,10 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>共青团中央、教育部、人力资源社会保障部、中国科协、 中国科学院、 中国社会科学院、中国工程院、全国学联、辽宁省人民政府 承办单位： 大连理工大学、共青团辽宁省委 二、竞赛主题 青春</t>
-        </is>
-      </c>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
+          <t>https://www.datafountain.cn/competitions/1098</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3977,37 +4390,37 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -4017,75 +4430,55 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>基于人工智能的闽江流域水情预报</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>中国商业统计学会</t>
-        </is>
-      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://www.datafountain.cn/competitions/1102</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4095,37 +4488,37 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4135,75 +4528,55 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>多模态BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>教育部高等学校电子商务类专业教学指导委员会</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.datafountain.cn/competitions/1104</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4213,37 +4586,37 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4253,121 +4626,97 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions/1153</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>部分赛道有奖金/扶持资源</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>教育部等部门</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://cy.ncss.cn/</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
           <t>P2 可选参加</t>
@@ -4375,75 +4724,55 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>获奖证书</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>共青团中央等单位</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4453,37 +4782,37 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -4493,63 +4822,55 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>种子数据</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>盲区突围：模型BadCase极限挑战赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>，东北林业大学承办，中国工商银行黑龙江省分行支持的第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛开幕式在东北林业大学举办</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://www.datafountain.cn/competitions/1097</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4559,84 +4880,84 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、数学建模、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>CCF BDCI</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4662,14 +4983,10 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛组织委员会</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
-        </is>
-      </c>
+          <t>中国统计教育学会</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>低</t>
@@ -4677,7 +4994,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4692,12 +5009,12 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -4707,17 +5024,17 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>94</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量、数学建模价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -4725,26 +5042,22 @@
           <t>种子数据</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
-        </is>
-      </c>
+      <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4754,7 +5067,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4764,7 +5077,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4780,12 +5093,12 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>共青团中央等单位</t>
+          <t>中国商业统计学会</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4795,47 +5108,47 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -4845,45 +5158,65 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>教育部高等学校电子商务类专业教学指导委员会</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4893,17 +5226,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -4928,59 +5261,59 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>商赛简历、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生创业服务网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4988,7 +5321,11 @@
           <t>以年度通知为准</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>部分赛道有奖金/扶持资源</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>获奖证书</t>
@@ -4996,12 +5333,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>高等学校大学外语教学研究会</t>
+          <t>教育部等部门</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5016,12 +5353,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -5046,12 +5383,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>含金量价值较高，建议优先跟进。</t>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -5061,19 +5398,19 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -5088,21 +5425,33 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026.06.19</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国科学院 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights</t>
+          <t>共青团中央等单位</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -5147,12 +5496,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -5162,7 +5511,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -5172,14 +5521,14 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5198,18 +5547,22 @@
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>，浙江工业大学承办</t>
+          <t>，东北林业大学承办，中国工商银行黑龙江省分行支持的第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛开幕式在东北林业大学举办</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5219,39 +5572,39 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
@@ -5274,44 +5627,60 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>中国大学生计算机设计大赛组织委员会</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5326,12 +5695,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -5346,12 +5715,12 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>84</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -5361,29 +5730,29 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>数据分析/量化、含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5398,34 +5767,38 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
-        </is>
-      </c>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
+          <t>获奖证书</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
+          <t>共青团中央等单位</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -5465,7 +5838,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -5480,7 +5853,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -5490,14 +5863,14 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（小挑）</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -5512,34 +5885,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>及良好市场潜力和发展前景的优秀项目，给予奖励；组织项目和成果的交流、展览、转化活动。在符合竞赛宗旨、具有良好导向的前提下，竞赛可设立专项赛事及配套交流活动，具体规则另行制定和颁布。 第四条 竞赛由校级、省级、全国三级赛制构成。校级初赛由各高</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>或专利技术所有人的书面授权许可、项目鉴定证书、专利证书等； （七）对于涉及已工商注册企业的项目，报名时应当提交相应证明材料（包括但不限于单位概况、法定代表人情况、加载统一社会信用代码的营业执照、股权结构等），项目负责人必须为企业法定代表人。</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5579,7 +5936,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -5594,54 +5951,70 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>全国大学生创业服务网</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>竞赛简介</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>通常每年春季初赛/决赛</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>获奖证书</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>的全国性的大学生课外学术实践竞赛，竞赛官方网站为 www.tiaozhanbei.net</t>
+          <t>高等学校大学外语教学研究会</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -5656,12 +6029,12 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -5681,7 +6054,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -5691,125 +6064,867 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+          <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>挑战杯官网</t>
+          <t>种子数据</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>共青团中央 教育部 人力资源社会保障部 中国科协 中国科学院 中国社会科学院 中国工程院 全国学联 辽宁省人民政府 Copyright © 2009-2025 All Rights</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>，浙江工业大学承办</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>的第十五届 “ 挑战杯 ”新疆维吾尔 自治区大学生创业计划竞赛决赛在伊犁师范大学成功举行</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯动态</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026.06.19</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>、实际应用价值和创新意义的优秀作品，给予奖励；组织学术交流和科技成果的展览、转让活动。 第二章 组织机构及其职责 第五条 竞赛设立领导小组，由主办单位和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>担申报作品60%以上的研究工作，作品鉴定证书、专利证书及发表的有关作品上的署名均应为第一作者，合作者必须是学生且不得超过2人；凡作者超过3人的项目或者不超过3人，但无法区分第一作者的项目，均须申报集体作品。集体作品的作者必须均为学生。凡有合</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>及良好市场潜力和发展前景的优秀项目，给予奖励；组织项目和成果的交流、展览、转化活动。在符合竞赛宗旨、具有良好导向的前提下，竞赛可设立专项赛事及配套交流活动，具体规则另行制定和颁布。 第四条 竞赛由校级、省级、全国三级赛制构成。校级初赛由各高</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>或专利技术所有人的书面授权许可、项目鉴定证书、专利证书等； （七）对于涉及已工商注册企业的项目，报名时应当提交相应证明材料（包括但不限于单位概况、法定代表人情况、加载统一社会信用代码的营业执照、股权结构等），项目负责人必须为企业法定代表人。</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>和承办单位的有关负责人组成，负责指导竞赛活动，并对全国组织委员会和全国评审委员会提交的问题进行协调和裁决</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>竞赛简介</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>的全国性的大学生课外学术实践竞赛，竞赛官方网站为 www.tiaozhanbei.net</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/focus</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>含金量、商赛简历价值较高，建议优先跟进。</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯官网</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>英语与财经表达类</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>含金量价值较高，建议优先跟进。</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>全国大学生英语竞赛</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X31"/>
+  <autoFilter ref="A1:X38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2440,7 +2440,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15843/</t>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3335,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3543,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3935,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4033,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4155,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4351,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4645,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4841,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4939,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5049,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5285,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5525,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5749,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5867,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5965,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6083,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6189,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6215,11 @@
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -6287,7 +6295,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6397,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6499,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6613,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6727,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6829,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6927,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2440,11 +2440,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15843/</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3433,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6215,11 +6211,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -6295,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2254,7 +2254,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -766,11 +766,15 @@
           <t>32</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -787,7 +791,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -802,38 +806,34 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>竞赛30周年视频</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/56839f97c847c3ab2646b42819446621.html</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3356,19 +3356,23 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会（CSIAM） 承办单位：CSIAM数学模型专业委员会（代章） 全国大学生数学建模竞赛组委会 太原理工大学 协办单位：山西省工业与应用数学学会 2026年5月</t>
+          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3433,14 +3437,14 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3455,26 +3459,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3539,14 +3535,14 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3572,7 +3568,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3637,14 +3633,14 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3670,7 +3666,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3735,14 +3731,14 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>竞赛30周年视频</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3768,7 +3764,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/56839f97c847c3ab2646b42819446621.html</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3833,7 +3829,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3927,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4025,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4147,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4245,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4343,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4441,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4539,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4637,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4735,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4833,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4931,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5041,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5277,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5399,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5517,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5859,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6075,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6181,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6283,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6385,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6487,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6601,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6715,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6817,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6915,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,12 +1921,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -968,7 +968,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>竞赛30周年视频</t>
+          <t>关于批准2025—2026年全国大学生数学建模赛题后续研究课题的通告</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/56839f97c847c3ab2646b42819446621.html</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/a423b01e1f2ed1a38e9741fc7703ee61.html</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>2026 6G/B6G 无线通信AI大赛</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>https://www.datafountain.cn/special/WAIC-20266GAI</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3731,14 +3731,14 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>竞赛30周年视频</t>
+          <t>关于批准2025—2026年全国大学生数学建模赛题后续研究课题的通告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/56839f97c847c3ab2646b42819446621.html</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/a423b01e1f2ed1a38e9741fc7703ee61.html</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AI赋能数据分析与应用赛</t>
+          <t>2026 6G/B6G 无线通信AI大赛</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1100</t>
+          <t>https://www.datafountain.cn/special/WAIC-20266GAI</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -4245,14 +4245,14 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>“睿创杯”第二届高校创新创业大赛</t>
+          <t>AI赋能数据分析与应用赛</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/special/dzjs</t>
+          <t>https://www.datafountain.cn/competitions/1100</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4293,19 +4293,19 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2440,7 +2440,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15843/</t>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3335,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3441,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5308,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5399,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6211,11 @@
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -6283,7 +6291,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6393,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6495,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6609,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6723,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6923,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2440,11 +2440,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15843/</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3535,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3633,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3731,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3829,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3927,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4025,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4147,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4245,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4343,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4441,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4539,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4637,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4735,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4833,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4931,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5041,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5277,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5304,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5403,7 +5399,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5517,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5623,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5741,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5859,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5957,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6075,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6181,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6211,11 +6207,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -6291,7 +6283,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6385,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6487,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6601,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6715,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6817,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6915,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
